--- a/extra-wishlist.xlsx
+++ b/extra-wishlist.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7F65953-CB56-4CC1-9153-B6BA0299C6E7}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A018ECA-6BF8-4447-BF97-808BC8A2F2B9}"/>
   <bookViews>
-    <workbookView xWindow="2573" yWindow="2573" windowWidth="21600" windowHeight="11452" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra Wishlist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$50</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="219" uniqueCount="178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="182">
   <si>
     <t>Image</t>
   </si>
@@ -573,6 +573,18 @@
   </si>
   <si>
     <t>TBD</t>
+  </si>
+  <si>
+    <t>UGOOS AM9 Pro</t>
+  </si>
+  <si>
+    <t>https://www.ugoos.shop/DE/ugoos-am9-pro-smart-tv-box-amlogic-s905x5-j-cortex-a510-lpddr5-4gb-64gb-wi-fi6-bt5-3-android-14-dolby-vision.html</t>
+  </si>
+  <si>
+    <t>240 EUR</t>
+  </si>
+  <si>
+    <t>https://www.ugoos.shop/media/catalog/product/cache/1074c0fa9dab7bb7ce0ca4d697318903/a/m/am9_pro.png</t>
   </si>
 </sst>
 </file>
@@ -951,16 +963,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E49"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="26.1328125" customWidth="1"/>
-    <col min="3" max="3" width="53.1328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.3984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="26.140625" customWidth="1"/>
+    <col min="3" max="3" width="53.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="79" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>3</v>
       </c>
@@ -977,7 +989,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>120</v>
       </c>
@@ -994,7 +1006,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>121</v>
       </c>
@@ -1011,7 +1023,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>45</v>
       </c>
@@ -1028,7 +1040,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>46</v>
       </c>
@@ -1045,7 +1057,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>87</v>
       </c>
@@ -1062,7 +1074,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>128</v>
       </c>
@@ -1079,7 +1091,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>61</v>
       </c>
@@ -1096,7 +1108,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -1110,7 +1122,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>176</v>
       </c>
@@ -1124,7 +1136,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>143</v>
       </c>
@@ -1138,7 +1150,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>61</v>
       </c>
@@ -1149,7 +1161,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>92</v>
       </c>
@@ -1163,7 +1175,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>153</v>
       </c>
@@ -1177,7 +1189,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>140</v>
       </c>
@@ -1191,7 +1203,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>163</v>
       </c>
@@ -1205,7 +1217,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>165</v>
       </c>
@@ -1219,7 +1231,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -1233,7 +1245,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>175</v>
       </c>
@@ -1247,7 +1259,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -1261,7 +1273,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>135</v>
       </c>
@@ -1278,7 +1290,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>73</v>
       </c>
@@ -1295,322 +1307,319 @@
         <v>111</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="E23" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>178</v>
+      </c>
+      <c r="B23" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" t="s">
+        <v>179</v>
+      </c>
+      <c r="D23" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E24" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>37</v>
       </c>
-      <c r="B24" t="s">
+      <c r="B25" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D24" t="s">
+      <c r="D25" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>21</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C26" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D25" t="s">
+      <c r="D26" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>64</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>62</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C27" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D26" t="s">
+      <c r="D27" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
         <v>108</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>109</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C28" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D28" t="s">
         <v>77</v>
       </c>
-      <c r="E27" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
+      <c r="E28" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>33</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>34</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>35</v>
       </c>
-      <c r="D28" t="s">
+      <c r="D29" t="s">
         <v>100</v>
-      </c>
-      <c r="E28" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" t="s">
-        <v>114</v>
-      </c>
-      <c r="C29" t="s">
-        <v>115</v>
-      </c>
-      <c r="D29" t="s">
-        <v>116</v>
       </c>
       <c r="E29" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>113</v>
+      </c>
+      <c r="B30" t="s">
+        <v>114</v>
+      </c>
+      <c r="C30" t="s">
+        <v>115</v>
+      </c>
+      <c r="D30" t="s">
+        <v>116</v>
+      </c>
+      <c r="E30" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>68</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>72</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>65</v>
       </c>
-      <c r="D30" t="s">
+      <c r="D31" t="s">
         <v>66</v>
       </c>
-      <c r="E30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
+      <c r="E31" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>67</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>69</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>70</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>71</v>
       </c>
-      <c r="E31" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
+      <c r="E32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
         <v>50</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>51</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>49</v>
       </c>
-      <c r="D32" t="s">
+      <c r="D33" t="s">
         <v>78</v>
       </c>
-      <c r="E32" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
+      <c r="E33" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
         <v>79</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>80</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>82</v>
       </c>
-      <c r="D33" t="s">
+      <c r="D34" t="s">
         <v>81</v>
       </c>
-      <c r="E33" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
+      <c r="E34" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
         <v>85</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>83</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>84</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>86</v>
       </c>
-      <c r="E34" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
+      <c r="E35" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
         <v>13</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>14</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C36" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D35" t="s">
+      <c r="D36" t="s">
         <v>91</v>
       </c>
-      <c r="E35" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="E36" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E37" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
         <v>4</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>5</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C38" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D37" t="s">
+      <c r="D38" t="s">
         <v>104</v>
       </c>
-      <c r="E37" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
+      <c r="E38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
         <v>7</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C39" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D38" t="s">
+      <c r="D39" t="s">
         <v>98</v>
       </c>
-      <c r="E38" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
+      <c r="E39" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
         <v>24</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>26</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C40" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="D39" t="s">
+      <c r="D40" t="s">
         <v>105</v>
       </c>
-      <c r="E39" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
+      <c r="E40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>27</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>28</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>29</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>106</v>
       </c>
-      <c r="E40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
+      <c r="E41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>52</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>53</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>54</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>107</v>
       </c>
-      <c r="E41" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" t="s">
-        <v>42</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="D42" t="s">
-        <v>103</v>
-      </c>
       <c r="E42" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D43" t="s">
         <v>103</v>
@@ -1619,118 +1628,135 @@
         <v>111</v>
       </c>
     </row>
-    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B44" t="s">
+        <v>43</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D44" t="s">
+        <v>103</v>
+      </c>
+      <c r="E44" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>30</v>
       </c>
-      <c r="B44" t="s">
+      <c r="B45" t="s">
         <v>31</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C45" t="s">
         <v>32</v>
       </c>
-      <c r="D44" t="s">
+      <c r="D45" t="s">
         <v>100</v>
       </c>
-      <c r="E44" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
+      <c r="E45" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
         <v>10</v>
       </c>
-      <c r="B45" t="s">
+      <c r="B46" t="s">
         <v>11</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C46" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>77</v>
       </c>
-      <c r="E45" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
+      <c r="E46" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>55</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>56</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>57</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>90</v>
       </c>
-      <c r="E46" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B47" t="s">
+      <c r="E47" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B48" t="s">
         <v>93</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>94</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>95</v>
       </c>
-      <c r="E47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="B48" t="s">
+      <c r="E48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B49" t="s">
         <v>16</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C49" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>102</v>
       </c>
-      <c r="E48" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
+      <c r="E49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
         <v>18</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>19</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C50" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>101</v>
       </c>
-      <c r="E49" t="s">
+      <c r="E50" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E49" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <autoFilter ref="A1:E50" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
     <filterColumn colId="4">
       <filters blank="1">
         <filter val="GAP"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A38:D40">
-    <sortCondition ref="D38:D40"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A39:D41">
+    <sortCondition ref="D39:D41"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
-    <hyperlink ref="C26" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
-    <hyperlink ref="C25" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
-    <hyperlink ref="C49" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
+    <hyperlink ref="C27" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
+    <hyperlink ref="C26" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="C50" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>

--- a/extra-wishlist.xlsx
+++ b/extra-wishlist.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0A018ECA-6BF8-4447-BF97-808BC8A2F2B9}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC4DA06-1857-4F85-BBAB-B0DC1F04FCB8}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra Wishlist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="190">
   <si>
     <t>Image</t>
   </si>
@@ -515,15 +515,6 @@
     <t>https://static01.galaxus.com/productimages/1/1/4/9/7/3/0/0/5/9/4/8/1/2/1/3/5/0/6/019a267c-c52a-7e01-b9f8-c15e936c5316_1000.avif</t>
   </si>
   <si>
-    <t>https://www.digitec.ch/en/s1/product/peak-design-everyday-sling-camera-shoulder-bag-6-l-camera-bag-60670840</t>
-  </si>
-  <si>
-    <t>https://static01.galaxus.com/productimages/3/0/5/0/4/0/6/4/0/3/2/9/6/9/5/2/7/8/4/019b149b-1fed-7cdd-9097-e23b3c7c18e8_1000.avif</t>
-  </si>
-  <si>
-    <t>129 CHF</t>
-  </si>
-  <si>
     <t>https://www.digitec.ch/en/s1/product/angelbird-av-pro-cfexpress-a-512-gb-cfexpress-type-a-memory-card-53079011</t>
   </si>
   <si>
@@ -566,9 +557,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>Geanta</t>
-  </si>
-  <si>
     <t>Macro Flash Kit</t>
   </si>
   <si>
@@ -585,6 +573,42 @@
   </si>
   <si>
     <t>https://www.ugoos.shop/media/catalog/product/cache/1074c0fa9dab7bb7ce0ca4d697318903/a/m/am9_pro.png</t>
+  </si>
+  <si>
+    <t>DJI RS 5 Combo</t>
+  </si>
+  <si>
+    <t>https://static01.galaxus.com/productimages/1/7/4/5/6/5/9/6/7/4/3/4/8/3/7/3/8/1/4/019df2b9-4a22-73f4-982b-0f560f9ebee0_2880.avif</t>
+  </si>
+  <si>
+    <t>https://www.digitec.ch/en/s1/product/dji-rs-5-combo-single-lens-reflex-camera-system-camera-3-kg-gimbal-65196566</t>
+  </si>
+  <si>
+    <t>625 CHF</t>
+  </si>
+  <si>
+    <t>https://www.dxo.com/en/dxo-photolab/</t>
+  </si>
+  <si>
+    <t>270 CHF</t>
+  </si>
+  <si>
+    <t>https://www.dxo.com/static/dxo.svg</t>
+  </si>
+  <si>
+    <t>DXO Photolab</t>
+  </si>
+  <si>
+    <t>PureRef Business</t>
+  </si>
+  <si>
+    <t>https://www.pureref.com/images/PureRef.svg</t>
+  </si>
+  <si>
+    <t>https://www.pureref.com/download.php</t>
+  </si>
+  <si>
+    <t>50 USD</t>
   </si>
 </sst>
 </file>
@@ -963,7 +987,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E50"/>
+  <dimension ref="A1:E52"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
@@ -1110,153 +1134,153 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>146</v>
+        <v>178</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>179</v>
       </c>
       <c r="C9" t="s">
-        <v>141</v>
+        <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>142</v>
+        <v>181</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="B10" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C10" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D10" t="s">
-        <v>148</v>
+        <v>183</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s">
-        <v>172</v>
+        <v>145</v>
       </c>
       <c r="C11" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="D11" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="B12" t="s">
-        <v>169</v>
+        <v>173</v>
+      </c>
+      <c r="C12" t="s">
+        <v>173</v>
       </c>
       <c r="D12" t="s">
-        <v>170</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="B13" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="C13" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="D13" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>153</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>151</v>
-      </c>
-      <c r="C14" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>140</v>
+        <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C15" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="D15" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>140</v>
       </c>
       <c r="B16" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C16" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D16" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="B17" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C17" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="D17" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>162</v>
       </c>
       <c r="B18" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="D18" t="s">
-        <v>95</v>
+        <v>165</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="B19" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C19" t="s">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="D19" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1270,7 +1294,7 @@
         <v>137</v>
       </c>
       <c r="D20" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
@@ -1309,162 +1333,156 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B23" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="C23" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D23" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E24" t="s">
+      <c r="A24" t="s">
+        <v>186</v>
+      </c>
+      <c r="B24" t="s">
+        <v>187</v>
+      </c>
+      <c r="C24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D24" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>37</v>
-      </c>
-      <c r="B25" t="s">
-        <v>36</v>
-      </c>
-      <c r="C25" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="B26" t="s">
-        <v>22</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>23</v>
+        <v>151</v>
+      </c>
+      <c r="C26" t="s">
+        <v>150</v>
       </c>
       <c r="D26" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D27" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
         <v>64</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B29" t="s">
         <v>62</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C29" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D27" t="s">
+      <c r="D29" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>108</v>
-      </c>
-      <c r="B28" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D28" t="s">
-        <v>77</v>
-      </c>
-      <c r="E28" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>33</v>
-      </c>
-      <c r="B29" t="s">
-        <v>34</v>
-      </c>
-      <c r="C29" t="s">
-        <v>35</v>
-      </c>
-      <c r="D29" t="s">
-        <v>100</v>
-      </c>
-      <c r="E29" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B30" t="s">
-        <v>114</v>
-      </c>
-      <c r="C30" t="s">
-        <v>115</v>
+        <v>109</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="D30" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="E30" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B31" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C31" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="D31" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="E31" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="B32" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="C32" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="E32" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C33" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D33" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E33" t="s">
         <v>111</v>
@@ -1472,16 +1490,16 @@
     </row>
     <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B34" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D34" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E34" t="s">
         <v>111</v>
@@ -1489,16 +1507,16 @@
     </row>
     <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="C35" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="D35" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E35" t="s">
         <v>111</v>
@@ -1506,72 +1524,72 @@
     </row>
     <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>15</v>
+        <v>80</v>
+      </c>
+      <c r="C36" t="s">
+        <v>82</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E36" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" t="s">
+        <v>84</v>
+      </c>
+      <c r="D37" t="s">
+        <v>86</v>
+      </c>
       <c r="E37" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D38" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E38" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>7</v>
-      </c>
-      <c r="B39" t="s">
-        <v>8</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" t="s">
-        <v>98</v>
-      </c>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E39" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B40" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E40" t="s">
         <v>111</v>
@@ -1579,16 +1597,16 @@
     </row>
     <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B41" t="s">
-        <v>28</v>
-      </c>
-      <c r="C41" t="s">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E41" t="s">
         <v>111</v>
@@ -1596,16 +1614,16 @@
     </row>
     <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B42" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" t="s">
-        <v>54</v>
+        <v>26</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D42" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E42" t="s">
         <v>111</v>
@@ -1613,16 +1631,16 @@
     </row>
     <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B43" t="s">
-        <v>42</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="C43" t="s">
+        <v>29</v>
       </c>
       <c r="D43" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E43" t="s">
         <v>111</v>
@@ -1630,16 +1648,16 @@
     </row>
     <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
+      </c>
+      <c r="C44" t="s">
+        <v>54</v>
       </c>
       <c r="D44" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E44" t="s">
         <v>111</v>
@@ -1647,16 +1665,16 @@
     </row>
     <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B45" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" t="s">
-        <v>32</v>
+        <v>42</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D45" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E45" t="s">
         <v>111</v>
@@ -1664,16 +1682,16 @@
     </row>
     <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B46" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D46" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="E46" t="s">
         <v>111</v>
@@ -1681,82 +1699,116 @@
     </row>
     <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
+        <v>30</v>
+      </c>
+      <c r="B47" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" t="s">
+        <v>32</v>
+      </c>
+      <c r="D47" t="s">
+        <v>100</v>
+      </c>
+      <c r="E47" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>10</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D48" t="s">
+        <v>77</v>
+      </c>
+      <c r="E48" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>55</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B49" t="s">
         <v>56</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C49" t="s">
         <v>57</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D49" t="s">
         <v>90</v>
       </c>
-      <c r="E47" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B48" t="s">
+      <c r="E49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
         <v>93</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C50" t="s">
         <v>94</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D50" t="s">
         <v>95</v>
       </c>
-      <c r="E48" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B49" t="s">
+      <c r="E50" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
         <v>16</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C51" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D51" t="s">
         <v>102</v>
       </c>
-      <c r="E49" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
+      <c r="E51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>18</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B52" t="s">
         <v>19</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C52" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D52" t="s">
         <v>101</v>
       </c>
-      <c r="E50" t="s">
+      <c r="E52" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E50" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <autoFilter ref="A1:E52" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
     <filterColumn colId="4">
       <filters blank="1">
         <filter val="GAP"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A39:D41">
-    <sortCondition ref="D39:D41"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A41:D43">
+    <sortCondition ref="D41:D43"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
-    <hyperlink ref="C27" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
-    <hyperlink ref="C26" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
-    <hyperlink ref="C50" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
+    <hyperlink ref="C29" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
+    <hyperlink ref="C28" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="C52" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>

--- a/extra-wishlist.xlsx
+++ b/extra-wishlist.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EC4DA06-1857-4F85-BBAB-B0DC1F04FCB8}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AAB7E34-C1DE-481B-9FDE-4D156EF85879}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra Wishlist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$52</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$54</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="198">
   <si>
     <t>Image</t>
   </si>
@@ -584,9 +584,6 @@
     <t>https://www.digitec.ch/en/s1/product/dji-rs-5-combo-single-lens-reflex-camera-system-camera-3-kg-gimbal-65196566</t>
   </si>
   <si>
-    <t>625 CHF</t>
-  </si>
-  <si>
     <t>https://www.dxo.com/en/dxo-photolab/</t>
   </si>
   <si>
@@ -609,6 +606,33 @@
   </si>
   <si>
     <t>50 USD</t>
+  </si>
+  <si>
+    <t>Nintendo Switch 2</t>
+  </si>
+  <si>
+    <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/61CIA5IVbvL._SL1500_.jpg</t>
+  </si>
+  <si>
+    <t>https://www.amazon.de/-/en/Nintendo-10015151-Switch-2/dp/B0F2J4SYJ2?crid=QWG2F2KE0LM8&amp;dib=eyJ2IjoiMSJ9.7NGB7_ult4EHlSi6pQT6yyW4NLq5ASsbRZvFk1TIGmwBSABVHVAlASOW1x90xr1NeeNLvQklfWvQEpmDOIoheUq9ovzAxKrKXWc2JYDdj4sszTSYW9zBWVF2nkh6xrWSwGVRqM5dZNwHKaIEPCQqwWNjP_mYH1iF3RSQLxhrEvU2NI4d8lVWWYYFzU5-aR8UVEfcoFrai7IcDz08_NYr-pUR-xc3T7ioTBmU2xf0T2o.-LKh_FJZV_VeHUY_ZRYM4zt1JkcuwqzghgKR7fI6RI0&amp;dib_tag=se&amp;keywords=nintendo+switch+2&amp;qid=1790145892&amp;sprefix=nintendo+switch+2+%2Caps%2C134&amp;sr=8-1</t>
+  </si>
+  <si>
+    <t>408 EUR</t>
+  </si>
+  <si>
+    <t>590 EUR</t>
+  </si>
+  <si>
+    <t>60 USD</t>
+  </si>
+  <si>
+    <t>https://nebula.tv/join?plan=yearly</t>
+  </si>
+  <si>
+    <t>data:image/png;base64,iVBORw0KGgoAAAANSUhEUgAAAIAAAACACAYAAADDPmHLAAAAGXRFWHRTb2Z0d2FyZQBBZG9iZSBJbWFnZVJlYWR5ccllPAAAA3ZpVFh0WE1MOmNvbS5hZG9iZS54bXAAAAAAADw/eHBhY2tldCBiZWdpbj0i77u/IiBpZD0iVzVNME1wQ2VoaUh6cmVTek5UY3prYzlkIj8+IDx4OnhtcG1ldGEgeG1sbnM6eD0iYWRvYmU6bnM6bWV0YS8iIHg6eG1wdGs9IkFkb2JlIFhNUCBDb3JlIDcuMC1jMDAwIDc5LmRhYmFjYmIsIDIwMjEvMDQvMTQtMDA6Mzk6NDQgICAgICAgICI+IDxyZGY6UkRGIHhtbG5zOnJkZj0iaHR0cDovL3d3dy53My5vcmcvMTk5OS8wMi8yMi1yZGYtc3ludGF4LW5zIyI+IDxyZGY6RGVzY3JpcHRpb24gcmRmOmFib3V0PSIiIHhtbG5zOnhtcE1NPSJodHRwOi8vbnMuYWRvYmUuY29tL3hhcC8xLjAvbW0vIiB4bWxuczpzdFJlZj0iaHR0cDovL25zLmFkb2JlLmNvbS94YXAvMS4wL3NUeXBlL1Jlc291cmNlUmVmIyIgeG1sbnM6eG1wPSJodHRwOi8vbnMuYWRvYmUuY29tL3hhcC8xLjAvIiB4bXBNTTpPcmlnaW5hbERvY3VtZW50SUQ9InhtcC5kaWQ6NDBkYTNiMDUtYjUxNC00MGNlLWE1MzAtYjA5MzViMGMzOTUzIiB4bXBNTTpEb2N1bWVudElEPSJ4bXAuZGlkOjFCNzdCRDZCRUVENDExRUJBNjI1RjQyQkI3MjBDNDY1IiB4bXBNTTpJbnN0YW5jZUlEPSJ4bXAuaWlkOjFCNzdCRDZBRUVENDExRUJBNjI1RjQyQkI3MjBDNDY1IiB4bXA6Q3JlYXRvclRvb2w9IkFkb2JlIFBob3Rvc2hvcCAyMS4wIChNYWNpbnRvc2gpIj4gPHhtcE1NOkRlcml2ZWRGcm9tIHN0UmVmOmluc3RhbmNlSUQ9InhtcC5paWQ6YjM0Y2EyYjUtOGRkYi00MjI3LTliMDAtNWRkM2U5OGVjODExIiBzdFJlZjpkb2N1bWVudElEPSJ4bXAuZGlkOjQwZGEzYjA1LWI1MTQtNDBjZS1hNTMwLWIwOTM1YjBjMzk1MyIvPiA8L3JkZjpEZXNjcmlwdGlvbj4gPC9yZGY6UkRGPiA8L3g6eG1wbWV0YT4gPD94cGFja2V0IGVuZD0iciI/Purz3kQAAAW6SURBVHja7J1biFVVGMfXMcfMqOyClV0MupndJKKwop6iCCOiwB5CopsJYoFEFtFjVESXl6Ib1UMXKM7MmE2m6UhlvRTZVdNIgyQipRvaoJOn72N/Q4fjnDnn7LPP3nut9fvBHxnPzN6Ltf7nW2t9a6+1K7VazUG8TKIKMABgAMAAgAEAAwAGAAwAGAAwAGAAwACAAQADAAYADAAYADAAYADAAIABAAMABgAMABgAMABgAMAAgAEAAwAGwKQ+lN2Hyj1RtFRU8azxl4hOLnshKx4cEHGQ6DPRr6LbRT+XvLwzRS+IZonmikaJAN3xr+gV0VWiT0XXlris11gZ9d9Xy974PvWvQ6J91h2sED0mOrhE5esTPSx618K+mnYlg5Ts2GrdwBj3itaJzi5B2WaLPhDdX/d/X4g2Y4BsGWj4+RLRBtGtBZZpoegT0eXjlLWGAbLlHQut9Rwhekn0sujIHMui933R+vnG+9asrMxTM2azhdbxuEX0seiyHMoxz+51W5PPvxJ9gwGyR79ZgxN8PsfGBff1sAzLRMOicyb4HR2k7scAvesGai1G44/Y72WZhDnB+vXH25h9DPpUob4Z4GtTK+bb4Oy6DO453+b27VzrO9GXGKB37LcQ2+m3dmqKe02piyYndRChRjFAb+k0xC6zscG5HfyNjifWphhPDPpWmT4aYKNoU8Yj98YZxYYUM4rGZBUG6BGjKefZh9fN3Y8a5/PpdTmF6Smur2ngfRggHwa6+NuF9g2vz95dahGim6xiv48VWfH0fQE6QPtWdFoX19Bvq+bvNbv4qF0zLdtFZ4lGfKvIyZ5GgL0Wcu/u4hp9NkPIgiEfG9/nLqBsIbff10qsePzKGJ3b6/rArILLsUN0hmgPESBfRiz0Fs0qXxvfdwOUJfRWfa7AiudvDTtU9L1L0r5FoA+qni76mwhQDLstBBfFap8bPwQDFN0NVH2vvEoAL448zCV5+GNzvu8ulySi/iACFIuG4IEC7rvC98YPxQBTbTCYN4eYMECB6Bq/rvXfXMC9bxKtF52PAYpB1/Z1BW9egWW4SPSRaBGDwPzQtfwnXbKsWyZeE90j2okBeoeu4T/nku1YZWSrRYNhuoDsWe6SPXizS1xGzQquET3oS936EAF0te8Zl2y59on3RYtF24gA6bneJc/3+9b4yth5BjdigHRz+ydckmqd6fFMRbOTb4meFk2jC2iP80TPiy52YaGPjN/pmm9wJQIId9i8OrTGVy4UfWjjAiJAA0eLnnLFZPSK4A2XPND6GwZw7gqb25/p4uIHyxmsi7UL0HP/HrC5fWyNr+hSsj5Q8lCR7VBUBDhF9KzoageKJo/uEv0YQwS4webHNP7/XGl1siBkA+hATzN6b4uOo80PYIboTZsCHxNiF3C86ALRPy6/I9Q0mTS3y2vogU9LcxwXTbNcwY48bpjn3sBfXLKfL09ez8AA+q0cdoES+vsC1HDdnNilkWplyBUUugE2ue5Sr+0eSoUBSkqrswVb4dWZfxigeSOmHXQOhl45MRggbRjX7mMjBvCfTs4WrMe7M/8wQLahfCCGionFABrKO3mBg67UfY4BwqHTswU1f7AXA4RFJyG9P5ZKCWF7eLvoOYB6mvepLX7vJ5fsPRghAoSFhvR20rpDsTR+bAZotxvoj6lCYuoClFZnC+oSrD6etpsIECYa2t+b4PNVMTV+jAZQqoT/eLsARY+T2eIO3HLm/Zl/RID2aHa24JrYGj9WAzTrBqoxVkSMXYCir4/R0zxm2M+7LPz/TgSIg79csitnjLUxNn7MBmgM+dVYKyHWLkDRt35vd8mj8ZoY2hljJUyOOAJoyNfjZ6bE2vixG0DRbWp9MVdAzF3A2GxAt2P9iQEgSiZRBRgAMABgAMAAgAEAAwAGAAwAGAAwAGAAwACAAQADAAYADAAYADAAYADAAIABAAOAz/wnwAAcPS/fE+WT5wAAAABJRU5ErkJggg==</t>
+  </si>
+  <si>
+    <t>Nebula TV 1yr</t>
   </si>
 </sst>
 </file>
@@ -687,6 +711,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -987,7 +1015,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E52"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
@@ -1143,380 +1171,374 @@
         <v>180</v>
       </c>
       <c r="D9" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B10" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="C10" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="D10" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>146</v>
+        <v>197</v>
       </c>
       <c r="B11" t="s">
-        <v>145</v>
+        <v>196</v>
       </c>
       <c r="C11" t="s">
-        <v>141</v>
+        <v>195</v>
       </c>
       <c r="D11" t="s">
-        <v>142</v>
+        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B12" t="s">
-        <v>173</v>
+        <v>183</v>
       </c>
       <c r="C12" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="D12" t="s">
-        <v>148</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="B13" t="s">
-        <v>169</v>
+        <v>145</v>
       </c>
       <c r="C13" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="D13" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>61</v>
+        <v>172</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>173</v>
+      </c>
+      <c r="C14" t="s">
+        <v>173</v>
       </c>
       <c r="D14" t="s">
-        <v>167</v>
+        <v>148</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>143</v>
       </c>
       <c r="B15" t="s">
-        <v>149</v>
+        <v>169</v>
       </c>
       <c r="C15" t="s">
-        <v>147</v>
+        <v>168</v>
       </c>
       <c r="D15" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>140</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>155</v>
-      </c>
-      <c r="C16" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="D16" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>160</v>
+        <v>92</v>
       </c>
       <c r="B17" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C17" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="D17" t="s">
-        <v>161</v>
+        <v>148</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>162</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="C18" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="D18" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>73</v>
+        <v>160</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="D19" t="s">
-        <v>95</v>
+        <v>161</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20" t="s">
+        <v>164</v>
+      </c>
+      <c r="C20" t="s">
+        <v>163</v>
+      </c>
+      <c r="D20" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>73</v>
+      </c>
+      <c r="B21" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
         <v>139</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B22" t="s">
         <v>138</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C22" t="s">
         <v>137</v>
       </c>
-      <c r="D20" t="s">
+      <c r="D22" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
         <v>135</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B23" t="s">
         <v>136</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C23" t="s">
         <v>133</v>
       </c>
-      <c r="D21" t="s">
+      <c r="D23" t="s">
         <v>134</v>
       </c>
-      <c r="E21" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="E23" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
         <v>73</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B24" t="s">
         <v>74</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C24" t="s">
         <v>75</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D24" t="s">
         <v>76</v>
       </c>
-      <c r="E22" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+      <c r="E24" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
         <v>174</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B25" t="s">
         <v>177</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C25" t="s">
         <v>175</v>
       </c>
-      <c r="D23" t="s">
+      <c r="D25" t="s">
         <v>176</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>186</v>
-      </c>
-      <c r="B24" t="s">
-        <v>187</v>
-      </c>
-      <c r="C24" t="s">
-        <v>188</v>
-      </c>
-      <c r="D24" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E25" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>153</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>186</v>
       </c>
       <c r="C26" t="s">
-        <v>150</v>
+        <v>187</v>
       </c>
       <c r="D26" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="D27" t="s">
-        <v>99</v>
+      <c r="E27" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>153</v>
       </c>
       <c r="B28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C28" s="1" t="s">
-        <v>23</v>
+        <v>151</v>
+      </c>
+      <c r="C28" t="s">
+        <v>150</v>
       </c>
       <c r="D28" t="s">
-        <v>98</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>21</v>
+      </c>
+      <c r="B30" t="s">
+        <v>22</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>64</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B31" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C31" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D31" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>108</v>
-      </c>
-      <c r="B30" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D30" t="s">
-        <v>77</v>
-      </c>
-      <c r="E30" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>33</v>
-      </c>
-      <c r="B31" t="s">
-        <v>34</v>
-      </c>
-      <c r="C31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D31" t="s">
-        <v>100</v>
-      </c>
-      <c r="E31" t="s">
-        <v>171</v>
       </c>
     </row>
     <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B32" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" t="s">
-        <v>115</v>
+        <v>109</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="D32" t="s">
-        <v>116</v>
+        <v>77</v>
       </c>
       <c r="E32" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="B33" t="s">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="C33" t="s">
-        <v>65</v>
+        <v>35</v>
       </c>
       <c r="D33" t="s">
-        <v>66</v>
+        <v>100</v>
       </c>
       <c r="E33" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>67</v>
+        <v>113</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>114</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>115</v>
       </c>
       <c r="D34" t="s">
-        <v>71</v>
+        <v>116</v>
       </c>
       <c r="E34" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B35" t="s">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="C35" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="D35" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="E35" t="s">
         <v>111</v>
@@ -1524,16 +1546,16 @@
     </row>
     <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="B36" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="C36" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="D36" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E36" t="s">
         <v>111</v>
@@ -1541,16 +1563,16 @@
     </row>
     <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="B37" t="s">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>49</v>
       </c>
       <c r="D37" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E37" t="s">
         <v>111</v>
@@ -1558,72 +1580,72 @@
     </row>
     <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>13</v>
+        <v>79</v>
       </c>
       <c r="B38" t="s">
-        <v>14</v>
-      </c>
-      <c r="C38" s="1" t="s">
-        <v>15</v>
+        <v>80</v>
+      </c>
+      <c r="C38" t="s">
+        <v>82</v>
       </c>
       <c r="D38" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="E38" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>85</v>
+      </c>
+      <c r="B39" t="s">
+        <v>83</v>
+      </c>
+      <c r="C39" t="s">
+        <v>84</v>
+      </c>
+      <c r="D39" t="s">
+        <v>86</v>
+      </c>
       <c r="E39" t="s">
-        <v>58</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="D40" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="E40" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>7</v>
-      </c>
-      <c r="B41" t="s">
-        <v>8</v>
-      </c>
-      <c r="C41" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D41" t="s">
-        <v>98</v>
-      </c>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E41" t="s">
-        <v>111</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="B42" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="E42" t="s">
         <v>111</v>
@@ -1631,16 +1653,16 @@
     </row>
     <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" t="s">
-        <v>29</v>
+        <v>8</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E43" t="s">
         <v>111</v>
@@ -1648,16 +1670,16 @@
     </row>
     <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" t="s">
-        <v>54</v>
+        <v>26</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D44" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E44" t="s">
         <v>111</v>
@@ -1665,16 +1687,16 @@
     </row>
     <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B45" t="s">
-        <v>42</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>40</v>
+        <v>28</v>
+      </c>
+      <c r="C45" t="s">
+        <v>29</v>
       </c>
       <c r="D45" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="E45" t="s">
         <v>111</v>
@@ -1682,16 +1704,16 @@
     </row>
     <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B46" t="s">
-        <v>43</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>39</v>
+        <v>53</v>
+      </c>
+      <c r="C46" t="s">
+        <v>54</v>
       </c>
       <c r="D46" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E46" t="s">
         <v>111</v>
@@ -1699,16 +1721,16 @@
     </row>
     <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B47" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" t="s">
-        <v>32</v>
+        <v>42</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>40</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E47" t="s">
         <v>111</v>
@@ -1716,16 +1738,16 @@
     </row>
     <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D48" t="s">
-        <v>77</v>
+        <v>103</v>
       </c>
       <c r="E48" t="s">
         <v>111</v>
@@ -1733,82 +1755,116 @@
     </row>
     <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
+        <v>30</v>
+      </c>
+      <c r="B49" t="s">
+        <v>31</v>
+      </c>
+      <c r="C49" t="s">
+        <v>32</v>
+      </c>
+      <c r="D49" t="s">
+        <v>100</v>
+      </c>
+      <c r="E49" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>10</v>
+      </c>
+      <c r="B50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D50" t="s">
+        <v>77</v>
+      </c>
+      <c r="E50" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>55</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B51" t="s">
         <v>56</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C51" t="s">
         <v>57</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D51" t="s">
         <v>90</v>
       </c>
-      <c r="E49" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B50" t="s">
+      <c r="E51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
         <v>93</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C52" t="s">
         <v>94</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D52" t="s">
         <v>95</v>
       </c>
-      <c r="E50" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B51" t="s">
+      <c r="E52" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
         <v>16</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C53" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D53" t="s">
         <v>102</v>
       </c>
-      <c r="E51" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
+      <c r="E53" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>18</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B54" t="s">
         <v>19</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D54" t="s">
         <v>101</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E54" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E52" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <autoFilter ref="A1:E54" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
     <filterColumn colId="4">
       <filters blank="1">
         <filter val="GAP"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A41:D43">
-    <sortCondition ref="D41:D43"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:D45">
+    <sortCondition ref="D43:D45"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
-    <hyperlink ref="C29" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
-    <hyperlink ref="C28" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
-    <hyperlink ref="C52" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
+    <hyperlink ref="C31" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
+    <hyperlink ref="C30" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="C54" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>

--- a/extra-wishlist.xlsx
+++ b/extra-wishlist.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a5351de14e4a67c9/Downloads/wishlist/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cfn7021\Downloads\wishlist\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{67D664F4-3EEE-407E-AED6-119C200FF399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AAB7E34-C1DE-481B-9FDE-4D156EF85879}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A58E0BA-7560-4A27-8BC5-691B8DFC42AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
+    <workbookView xWindow="5910" yWindow="3390" windowWidth="21600" windowHeight="12645" xr2:uid="{FE4DC328-739C-48AF-B2EF-9BDF321350CE}"/>
   </bookViews>
   <sheets>
     <sheet name="Extra Wishlist" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Extra Wishlist'!$A$1:$E$55</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="239" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="202">
   <si>
     <t>Image</t>
   </si>
@@ -633,6 +633,18 @@
   </si>
   <si>
     <t>Nebula TV 1yr</t>
+  </si>
+  <si>
+    <t>Lanterna SK05 Pro 2 UV Mao White Flat</t>
+  </si>
+  <si>
+    <t>https://loopgear.com/cdn/shop/files/11_1_f7624e4d-2b6a-479c-adc7-e82a99d97607.jpg?v=1780971587&amp;width=876</t>
+  </si>
+  <si>
+    <t>https://loopgear.com/products/loop-gear-sk05-pro-2-uv-black-flat-led-flashlight?variant=59838698651934</t>
+  </si>
+  <si>
+    <t>121 USD</t>
   </si>
 </sst>
 </file>
@@ -711,10 +723,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1015,7 +1023,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
   <sheetPr filterMode="1"/>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="26.140625" customWidth="1"/>
@@ -1416,112 +1424,109 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E27" t="s">
+      <c r="A27" t="s">
+        <v>198</v>
+      </c>
+      <c r="B27" t="s">
+        <v>199</v>
+      </c>
+      <c r="C27" t="s">
+        <v>200</v>
+      </c>
+      <c r="D27" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E28" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>153</v>
-      </c>
-      <c r="B28" t="s">
-        <v>151</v>
-      </c>
-      <c r="C28" t="s">
-        <v>150</v>
-      </c>
-      <c r="D28" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>37</v>
+        <v>153</v>
       </c>
       <c r="B29" t="s">
-        <v>36</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>38</v>
+        <v>151</v>
+      </c>
+      <c r="C29" t="s">
+        <v>150</v>
       </c>
       <c r="D29" t="s">
-        <v>99</v>
+        <v>152</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>37</v>
       </c>
       <c r="B30" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D30" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="B31" t="s">
+        <v>22</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D31" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>64</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>62</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C32" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D31" t="s">
+      <c r="D32" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>108</v>
-      </c>
-      <c r="B32" t="s">
-        <v>109</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="D32" t="s">
-        <v>77</v>
-      </c>
-      <c r="E32" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="B33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>35</v>
+        <v>109</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="E33" t="s">
-        <v>171</v>
+        <v>111</v>
       </c>
     </row>
     <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>114</v>
+        <v>34</v>
       </c>
       <c r="C34" t="s">
-        <v>115</v>
+        <v>35</v>
       </c>
       <c r="D34" t="s">
-        <v>116</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
         <v>171</v>
@@ -1529,33 +1534,33 @@
     </row>
     <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>68</v>
+        <v>113</v>
       </c>
       <c r="B35" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="C35" t="s">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="D35" t="s">
-        <v>66</v>
+        <v>116</v>
       </c>
       <c r="E35" t="s">
-        <v>111</v>
+        <v>171</v>
       </c>
     </row>
     <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B36" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="E36" t="s">
         <v>111</v>
@@ -1563,16 +1568,16 @@
     </row>
     <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="B37" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C37" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="D37" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E37" t="s">
         <v>111</v>
@@ -1580,16 +1585,16 @@
     </row>
     <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="B38" t="s">
-        <v>80</v>
+        <v>51</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="D38" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="E38" t="s">
         <v>111</v>
@@ -1597,16 +1602,16 @@
     </row>
     <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B39" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C39" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D39" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E39" t="s">
         <v>111</v>
@@ -1614,55 +1619,55 @@
     </row>
     <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>85</v>
+      </c>
+      <c r="B40" t="s">
+        <v>83</v>
+      </c>
+      <c r="C40" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
         <v>13</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>14</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C41" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D40" t="s">
+      <c r="D41" t="s">
         <v>91</v>
       </c>
-      <c r="E40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E41" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E42" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>4</v>
-      </c>
-      <c r="B42" t="s">
-        <v>5</v>
-      </c>
-      <c r="C42" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" t="s">
-        <v>104</v>
-      </c>
-      <c r="E42" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="43" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B43" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D43" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E43" t="s">
         <v>111</v>
@@ -1670,16 +1675,16 @@
     </row>
     <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B44" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="D44" t="s">
-        <v>105</v>
+        <v>98</v>
       </c>
       <c r="E44" t="s">
         <v>111</v>
@@ -1687,16 +1692,16 @@
     </row>
     <row r="45" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>28</v>
-      </c>
-      <c r="C45" t="s">
-        <v>29</v>
+        <v>26</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>25</v>
       </c>
       <c r="D45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E45" t="s">
         <v>111</v>
@@ -1704,16 +1709,16 @@
     </row>
     <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="B46" t="s">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="C46" t="s">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="D46" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E46" t="s">
         <v>111</v>
@@ -1721,16 +1726,16 @@
     </row>
     <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>40</v>
+        <v>53</v>
+      </c>
+      <c r="C47" t="s">
+        <v>54</v>
       </c>
       <c r="D47" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E47" t="s">
         <v>111</v>
@@ -1741,10 +1746,10 @@
         <v>41</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D48" t="s">
         <v>103</v>
@@ -1755,16 +1760,16 @@
     </row>
     <row r="49" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="B49" t="s">
-        <v>31</v>
-      </c>
-      <c r="C49" t="s">
-        <v>32</v>
+        <v>43</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>39</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="E49" t="s">
         <v>111</v>
@@ -1772,16 +1777,16 @@
     </row>
     <row r="50" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="B50" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="1" t="s">
-        <v>12</v>
+        <v>31</v>
+      </c>
+      <c r="C50" t="s">
+        <v>32</v>
       </c>
       <c r="D50" t="s">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="E50" t="s">
         <v>111</v>
@@ -1789,30 +1794,33 @@
     </row>
     <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>10</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D51" t="s">
+        <v>77</v>
+      </c>
+      <c r="E51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
         <v>55</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>56</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>57</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>90</v>
-      </c>
-      <c r="E51" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="B52" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" t="s">
-        <v>94</v>
-      </c>
-      <c r="D52" t="s">
-        <v>95</v>
       </c>
       <c r="E52" t="s">
         <v>111</v>
@@ -1820,51 +1828,65 @@
     </row>
     <row r="53" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" t="s">
+        <v>94</v>
+      </c>
+      <c r="D53" t="s">
+        <v>95</v>
+      </c>
+      <c r="E53" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>16</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C54" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>102</v>
       </c>
-      <c r="E53" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
+      <c r="E54" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
         <v>18</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D54" t="s">
+      <c r="D55" t="s">
         <v>101</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E55" t="s">
         <v>111</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E54" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
+  <autoFilter ref="A1:E55" xr:uid="{2CF9E297-72DE-4386-8002-570237626454}">
     <filterColumn colId="4">
       <filters blank="1">
         <filter val="GAP"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A43:D45">
-    <sortCondition ref="D43:D45"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A44:D46">
+    <sortCondition ref="D44:D46"/>
   </sortState>
   <hyperlinks>
     <hyperlink ref="B8" r:id="rId1" xr:uid="{500C5F17-CD73-4F5C-9DAB-95952E174299}"/>
-    <hyperlink ref="C31" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
-    <hyperlink ref="C30" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
-    <hyperlink ref="C54" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
+    <hyperlink ref="C32" r:id="rId2" xr:uid="{376E2B05-F6F5-4BD7-87DB-872DA36FAD68}"/>
+    <hyperlink ref="C31" r:id="rId3" xr:uid="{EF3D4946-6DF4-4D31-8897-7C887F831DBF}"/>
+    <hyperlink ref="C55" r:id="rId4" xr:uid="{70AAF641-556E-4186-A150-1E8C658BA2FE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId5"/>
